--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_RECUCYM BAZU.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_RECUCYM BAZU.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>15.1639</v>
+        <v>23.9817</v>
       </c>
       <c r="E2" t="n">
-        <v>10.425</v>
+        <v>19.8577</v>
       </c>
       <c r="F2" t="n">
-        <v>4.738899999999999</v>
+        <v>4.124299999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>7.9851</v>
+        <v>15.8251</v>
       </c>
       <c r="H2" t="n">
-        <v>10.4425</v>
+        <v>20.2392</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.4576</v>
+        <v>-4.414000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>11.19</v>
+        <v>32.7257</v>
       </c>
       <c r="K2" t="n">
-        <v>12.9966</v>
+        <v>33.3178</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.8067</v>
+        <v>-0.5923000000000009</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.205</v>
+        <v>-16.9003</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.5541</v>
+        <v>-13.0788</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6509</v>
+        <v>-3.821800000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9702</v>
+        <v>-5.238899999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.597099999999999</v>
+        <v>-45.5979</v>
       </c>
       <c r="R2" t="n">
-        <v>7.567299999999999</v>
+        <v>40.3587</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5057</v>
+        <v>1.5086</v>
       </c>
       <c r="T2" t="n">
-        <v>5.177</v>
+        <v>-2.9353</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3288</v>
+        <v>4.4439</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7029000000000001</v>
+        <v>11.8871</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6551</v>
+        <v>35.6652</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04779999999999995</v>
+        <v>-23.7784</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>13.3047</v>
+        <v>11.2376</v>
       </c>
       <c r="E3" t="n">
-        <v>12.8506</v>
+        <v>6.9215</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4541000000000007</v>
+        <v>4.316</v>
       </c>
       <c r="G3" t="n">
-        <v>15.8251</v>
+        <v>7.9851</v>
       </c>
       <c r="H3" t="n">
-        <v>20.2392</v>
+        <v>10.4425</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.414000000000001</v>
+        <v>-2.4576</v>
       </c>
       <c r="J3" t="n">
-        <v>32.7257</v>
+        <v>11.19</v>
       </c>
       <c r="K3" t="n">
-        <v>33.3178</v>
+        <v>12.9966</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5923000000000009</v>
+        <v>-1.8067</v>
       </c>
       <c r="M3" t="n">
-        <v>-16.9003</v>
+        <v>-3.205</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.0788</v>
+        <v>-2.5541</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.821800000000001</v>
+        <v>-0.6509</v>
       </c>
       <c r="P3" t="n">
-        <v>-5.238899999999999</v>
+        <v>0.9702</v>
       </c>
       <c r="Q3" t="n">
-        <v>-45.5979</v>
+        <v>-6.597099999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>40.3587</v>
+        <v>7.567299999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>-9.168699999999999</v>
+        <v>1.5795</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.942299999999999</v>
+        <v>1.6735</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7736</v>
+        <v>-0.09399999999999997</v>
       </c>
       <c r="V3" t="n">
-        <v>11.8871</v>
+        <v>0.7029000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>35.6652</v>
+        <v>0.6551</v>
       </c>
       <c r="X3" t="n">
-        <v>-23.7784</v>
+        <v>0.04779999999999995</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MENDOZA ALVAREZ</t>
+          <t>S. MOYER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6.015400000000001</v>
+        <v>6.8079</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3503</v>
+        <v>13.8648</v>
       </c>
       <c r="F4" t="n">
-        <v>3.665</v>
+        <v>-7.0569</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8542000000000001</v>
+        <v>6.5697</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1489</v>
+        <v>1.2136</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2946</v>
+        <v>5.3561</v>
       </c>
       <c r="J4" t="n">
-        <v>3.795</v>
+        <v>17.0399</v>
       </c>
       <c r="K4" t="n">
-        <v>8.2637</v>
+        <v>4.1483</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.4686</v>
+        <v>12.8917</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9407</v>
+        <v>-10.4703</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.1148</v>
+        <v>-2.9347</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1742</v>
+        <v>-7.535600000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-19.9854</v>
+        <v>-0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>-30.4631</v>
+        <v>-6.7911</v>
       </c>
       <c r="R4" t="n">
-        <v>10.478</v>
+        <v>6.597099999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>19.5297</v>
+        <v>-1.6769</v>
       </c>
       <c r="T4" t="n">
-        <v>13.0695</v>
+        <v>-1.5616</v>
       </c>
       <c r="U4" t="n">
-        <v>6.4603</v>
+        <v>-0.1153</v>
       </c>
       <c r="V4" t="n">
-        <v>5.6165</v>
+        <v>2.1092</v>
       </c>
       <c r="W4" t="n">
-        <v>15.949</v>
+        <v>5.1776</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.3326</v>
+        <v>-3.0684</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>N. LAGNIEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6237</v>
+        <v>-2.2412</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8423</v>
+        <v>-3.539099999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>5.465699999999999</v>
+        <v>1.2979</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.2224</v>
+        <v>-2.9304</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1353000000000002</v>
+        <v>-2.4905</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.357600000000001</v>
+        <v>-0.4398999999999998</v>
       </c>
       <c r="J5" t="n">
-        <v>16.4491</v>
+        <v>-1.8362</v>
       </c>
       <c r="K5" t="n">
-        <v>15.58</v>
+        <v>-1.8413</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8693999999999997</v>
+        <v>0.005099999999999993</v>
       </c>
       <c r="M5" t="n">
-        <v>-24.6715</v>
+        <v>-1.0942</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.4447</v>
+        <v>-0.6493</v>
       </c>
       <c r="O5" t="n">
-        <v>-9.2271</v>
+        <v>-0.445</v>
       </c>
       <c r="P5" t="n">
-        <v>-27.9409</v>
+        <v>1.5523</v>
       </c>
       <c r="Q5" t="n">
-        <v>-59.762</v>
+        <v>-1.1642</v>
       </c>
       <c r="R5" t="n">
-        <v>31.8212</v>
+        <v>2.7165</v>
       </c>
       <c r="S5" t="n">
-        <v>24.1766</v>
+        <v>1.0206</v>
       </c>
       <c r="T5" t="n">
-        <v>10.9783</v>
+        <v>-0.1609999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>13.1981</v>
+        <v>1.1816</v>
       </c>
       <c r="V5" t="n">
-        <v>15.6102</v>
+        <v>-1.8836</v>
       </c>
       <c r="W5" t="n">
-        <v>30.4923</v>
+        <v>-0.3775999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-14.8822</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MOYER</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4266</v>
+        <v>-4.010600000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>11.5625</v>
+        <v>-23.3745</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.135899999999999</v>
+        <v>19.3642</v>
       </c>
       <c r="G6" t="n">
-        <v>6.5697</v>
+        <v>16.2754</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2136</v>
+        <v>4.982800000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3561</v>
+        <v>11.2931</v>
       </c>
       <c r="J6" t="n">
-        <v>17.0399</v>
+        <v>25.4223</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1483</v>
+        <v>17.3592</v>
       </c>
       <c r="L6" t="n">
-        <v>12.8917</v>
+        <v>8.0631</v>
       </c>
       <c r="M6" t="n">
-        <v>-10.4703</v>
+        <v>-9.146599999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.9347</v>
+        <v>-12.3768</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.535600000000001</v>
+        <v>3.2298</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.194</v>
+        <v>-14.3587</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.7911</v>
+        <v>-50.06059999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>6.597099999999999</v>
+        <v>35.702</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.058199999999999</v>
+        <v>6.0202</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.8639</v>
+        <v>-0.3770000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1945</v>
+        <v>6.3972</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1092</v>
+        <v>-11.948</v>
       </c>
       <c r="W6" t="n">
-        <v>5.1776</v>
+        <v>1.6402</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.0684</v>
+        <v>-13.5882</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. LAGNIEZ</t>
+          <t>J. MENDOZA ALVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7354000000000007</v>
+        <v>-4.139200000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9385</v>
+        <v>-5.857799999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.203</v>
+        <v>1.7187</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.9304</v>
+        <v>0.8542000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4905</v>
+        <v>3.1489</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4398999999999998</v>
+        <v>-2.2946</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8362</v>
+        <v>3.795</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8413</v>
+        <v>8.2637</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005099999999999993</v>
+        <v>-4.4686</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0942</v>
+        <v>-2.9407</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6493</v>
+        <v>-5.1148</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.445</v>
+        <v>2.1742</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5523</v>
+        <v>-19.9854</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1642</v>
+        <v>-30.4631</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7165</v>
+        <v>10.478</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5263</v>
+        <v>9.375400000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4396</v>
+        <v>4.8614</v>
       </c>
       <c r="U7" t="n">
-        <v>2.0866</v>
+        <v>4.514</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8836</v>
+        <v>5.6165</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3775999999999999</v>
+        <v>15.949</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.506</v>
+        <v>-10.3326</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.237600000000001</v>
+        <v>-4.634700000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.5206</v>
+        <v>-15.2193</v>
       </c>
       <c r="F8" t="n">
-        <v>9.2827</v>
+        <v>10.5849</v>
       </c>
       <c r="G8" t="n">
         <v>6.795399999999999</v>
@@ -1078,13 +1078,13 @@
         <v>42.1052</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4617</v>
+        <v>7.0645</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3440999999999999</v>
+        <v>0.9571999999999998</v>
       </c>
       <c r="U8" t="n">
-        <v>4.8055</v>
+        <v>6.1073</v>
       </c>
       <c r="V8" t="n">
         <v>6.7296</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. DE LA CRUZ DE LA ROSA</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.580000000000002</v>
+        <v>-7.9719</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.9441</v>
+        <v>-9.1495</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3639</v>
+        <v>1.177599999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-7.264500000000001</v>
+        <v>-8.2224</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8654</v>
+        <v>0.1353000000000002</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.399000000000001</v>
+        <v>-8.357600000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9539</v>
+        <v>16.4491</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1978</v>
+        <v>15.58</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.152000000000001</v>
+        <v>0.8693999999999997</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.3104</v>
+        <v>-24.6715</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.0634</v>
+        <v>-15.4447</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.246900000000001</v>
+        <v>-9.2271</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.2686</v>
+        <v>-27.9409</v>
       </c>
       <c r="Q9" t="n">
-        <v>-18.2392</v>
+        <v>-59.762</v>
       </c>
       <c r="R9" t="n">
-        <v>13.9703</v>
+        <v>31.8212</v>
       </c>
       <c r="S9" t="n">
-        <v>7.4978</v>
+        <v>12.5809</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7565</v>
+        <v>3.671</v>
       </c>
       <c r="U9" t="n">
-        <v>4.7413</v>
+        <v>8.909800000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.5447</v>
+        <v>15.6102</v>
       </c>
       <c r="W9" t="n">
-        <v>6.492500000000001</v>
+        <v>30.4923</v>
       </c>
       <c r="X9" t="n">
-        <v>-11.0372</v>
+        <v>-14.8822</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.1622</v>
+        <v>-9.3895</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.130700000000001</v>
+        <v>-9.731300000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.03140000000000021</v>
+        <v>0.3418000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-8.435</v>
@@ -1234,13 +1234,13 @@
         <v>4.0747</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9389000000000001</v>
+        <v>-1.1664</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8299</v>
+        <v>0.2293</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7688</v>
+        <v>-1.3957</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5642</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.4028</v>
+        <v>-9.5284</v>
       </c>
       <c r="E11" t="n">
-        <v>-30.7819</v>
+        <v>-4.201199999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>19.379</v>
+        <v>-5.327</v>
       </c>
       <c r="G11" t="n">
-        <v>16.2754</v>
+        <v>0.3899000000000006</v>
       </c>
       <c r="H11" t="n">
-        <v>4.982800000000001</v>
+        <v>0.8123999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>11.2931</v>
+        <v>-0.4225000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>25.4223</v>
+        <v>13.8723</v>
       </c>
       <c r="K11" t="n">
-        <v>17.3592</v>
+        <v>6.0802</v>
       </c>
       <c r="L11" t="n">
-        <v>8.0631</v>
+        <v>7.791899999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.146599999999999</v>
+        <v>-13.4823</v>
       </c>
       <c r="N11" t="n">
-        <v>-12.3768</v>
+        <v>-5.2678</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2298</v>
+        <v>-8.214300000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-14.3587</v>
+        <v>-6.5971</v>
       </c>
       <c r="Q11" t="n">
-        <v>-50.06059999999999</v>
+        <v>-22.314</v>
       </c>
       <c r="R11" t="n">
-        <v>35.702</v>
+        <v>15.7167</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3724</v>
+        <v>-1.2137</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.784400000000001</v>
+        <v>-0.794</v>
       </c>
       <c r="U11" t="n">
-        <v>6.4122</v>
+        <v>-0.4198</v>
       </c>
       <c r="V11" t="n">
-        <v>-11.948</v>
+        <v>-2.1074</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6402</v>
+        <v>5.0344</v>
       </c>
       <c r="X11" t="n">
-        <v>-13.5882</v>
+        <v>-7.141700000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>L. DE LA CRUZ DE LA ROSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.6501</v>
+        <v>-12.0087</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.101999999999999</v>
+        <v>-13.5467</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.548100000000001</v>
+        <v>1.5382</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3899000000000006</v>
+        <v>-7.264500000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8123999999999999</v>
+        <v>-2.8654</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4225000000000001</v>
+        <v>-4.399000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>13.8723</v>
+        <v>-1.9539</v>
       </c>
       <c r="K12" t="n">
-        <v>6.0802</v>
+        <v>0.1978</v>
       </c>
       <c r="L12" t="n">
-        <v>7.791899999999999</v>
+        <v>-2.152000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-13.4823</v>
+        <v>-5.3104</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.2678</v>
+        <v>-3.0634</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.214300000000001</v>
+        <v>-2.246900000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.5971</v>
+        <v>-4.2686</v>
       </c>
       <c r="Q12" t="n">
-        <v>-22.314</v>
+        <v>-18.2392</v>
       </c>
       <c r="R12" t="n">
-        <v>15.7167</v>
+        <v>13.9703</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.335699999999999</v>
+        <v>4.069</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6949</v>
+        <v>0.1539000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.6404</v>
+        <v>3.9153</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1074</v>
+        <v>-4.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>5.0344</v>
+        <v>6.492500000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.141700000000001</v>
+        <v>-11.0372</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.8882</v>
+        <v>-12.9708</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.4931</v>
+        <v>-13.0907</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3951</v>
+        <v>0.1199000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9639</v>
@@ -1468,13 +1468,13 @@
         <v>8.1493</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.7603</v>
+        <v>-1.8428</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.8187</v>
+        <v>-2.4163</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9418</v>
+        <v>0.5732</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6717</v>
@@ -1501,13 +1501,13 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.4907</v>
+        <v>-14.5088</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.123</v>
+        <v>-21.2231</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6324</v>
+        <v>6.7141</v>
       </c>
       <c r="G14" t="n">
         <v>-9.704600000000001</v>
@@ -1546,13 +1546,13 @@
         <v>35.5081</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0739</v>
+        <v>3.9077</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8514</v>
+        <v>0.7513000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.9254</v>
+        <v>3.1562</v>
       </c>
       <c r="V14" t="n">
         <v>-8.712300000000001</v>
@@ -1579,13 +1579,13 @@
         <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.3271</v>
+        <v>-22.3635</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.101</v>
+        <v>-15.5003</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.226099999999999</v>
+        <v>-6.8632</v>
       </c>
       <c r="G15" t="n">
         <v>-15.4662</v>
@@ -1624,13 +1624,13 @@
         <v>4.2687</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9307999999999998</v>
+        <v>1.0322</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7796</v>
+        <v>-0.179</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1513</v>
+        <v>1.2113</v>
       </c>
       <c r="V15" t="n">
         <v>-3.6613</v>
@@ -1657,13 +1657,13 @@
         <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-36.6598</v>
+        <v>-36.1507</v>
       </c>
       <c r="E16" t="n">
-        <v>-31.7276</v>
+        <v>-34.3302</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.9326</v>
+        <v>-1.8206</v>
       </c>
       <c r="G16" t="n">
         <v>-14.0706</v>
@@ -1702,13 +1702,13 @@
         <v>15.1345</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8592000000000005</v>
+        <v>1.3684</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3594</v>
+        <v>-0.2432</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.5006</v>
+        <v>1.6116</v>
       </c>
       <c r="V16" t="n">
         <v>-9.478400000000001</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-50.78879999999999</v>
+        <v>-42.4826</v>
       </c>
       <c r="E17" t="n">
-        <v>-45.9722</v>
+        <v>-42.3686</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.816800000000001</v>
+        <v>-0.1137000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-6.5441</v>
@@ -1780,13 +1780,13 @@
         <v>32.4035</v>
       </c>
       <c r="S17" t="n">
-        <v>-9.5829</v>
+        <v>-1.2762</v>
       </c>
       <c r="T17" t="n">
-        <v>-6.046</v>
+        <v>-2.4424</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.5372</v>
+        <v>1.1659</v>
       </c>
       <c r="V17" t="n">
         <v>-12.3482</v>
@@ -1813,22 +1813,22 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-156.3884</v>
+        <v>-140.3734</v>
       </c>
       <c r="E18" t="n">
-        <v>-170.4886</v>
+        <v>-170.4883</v>
       </c>
       <c r="F18" t="n">
-        <v>14.0987</v>
+        <v>30.1162</v>
       </c>
       <c r="G18" t="n">
-        <v>-22.90690000000001</v>
+        <v>-22.9069</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.770399999999999</v>
+        <v>-1.770400000000002</v>
       </c>
       <c r="I18" t="n">
-        <v>-21.13460000000001</v>
+        <v>-21.1346</v>
       </c>
       <c r="J18" t="n">
         <v>143.0339</v>
@@ -1846,7 +1846,7 @@
         <v>-115.2967</v>
       </c>
       <c r="O18" t="n">
-        <v>-50.64330000000001</v>
+        <v>-50.6433</v>
       </c>
       <c r="P18" t="n">
         <v>-144.5548</v>
@@ -1858,16 +1858,16 @@
         <v>306.5718</v>
       </c>
       <c r="S18" t="n">
-        <v>26.3352</v>
+        <v>42.351</v>
       </c>
       <c r="T18" t="n">
-        <v>1.187699999999999</v>
+        <v>1.187799999999998</v>
       </c>
       <c r="U18" t="n">
-        <v>25.1464</v>
+        <v>41.16250000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-15.26430000000001</v>
+        <v>-15.2643</v>
       </c>
       <c r="W18" t="n">
         <v>136.4152</v>
